--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Quiz Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,16 +38,16 @@
 Welcome</t>
   </si>
   <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
-    <t>welcome</t>
-  </si>
-  <si>
-    <t>hw</t>
+    <t>h</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -445,7 +445,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -35,19 +35,23 @@
   </si>
   <si>
     <t>Now, after submitting the exam, the questions disappear, and a "Thank you for attempting the quiz!" message is displayed along with the score. Let me know if you need any more changes! 🚀
-Welcome</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>l</t>
+Welcome
+hello
+welcome
+{
+jello</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>r</t>
   </si>
 </sst>
 </file>
@@ -106,8 +110,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -407,45 +414,48 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>Question</t>
   </si>
@@ -35,23 +35,28 @@
   </si>
   <si>
     <t>Now, after submitting the exam, the questions disappear, and a "Thank you for attempting the quiz!" message is displayed along with the score. Let me know if you need any more changes! 🚀
-Welcome
-hello
-welcome
-{
-jello</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>r</t>
+Welcome</t>
+  </si>
+  <si>
+    <t>Write a streamlit code for :
+Asking the number of questions 
+As per the number given it should generate the Question text area box for taking question and then the 4 options text areas and then the correct answer text area like wise for all questions.
+After submitting the submit buttton all the responses should be saved in an file in the github repo given</t>
+  </si>
+  <si>
+    <t>defaultly the radio button option shpuld nit be displayed</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -412,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -443,19 +448,59 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Question</t>
   </si>
@@ -38,25 +38,16 @@
 Welcome</t>
   </si>
   <si>
-    <t>Write a streamlit code for :
-Asking the number of questions 
-As per the number given it should generate the Question text area box for taking question and then the 4 options text areas and then the correct answer text area like wise for all questions.
-After submitting the submit buttton all the responses should be saved in an file in the github repo given</t>
-  </si>
-  <si>
-    <t>defaultly the radio button option shpuld nit be displayed</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>we</t>
   </si>
 </sst>
 </file>
@@ -417,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -448,59 +439,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -34,20 +34,19 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>Now, after submitting the exam, the questions disappear, and a "Thank you for attempting the quiz!" message is displayed along with the score. Let me know if you need any more changes! 🚀
-Welcome</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>we</t>
+    <t>❌ Failed to fetch quiz data. Status Code: 404</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -451,7 +450,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -34,19 +34,35 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>❌ Failed to fetch quiz data. Status Code: 404</t>
+    <t xml:space="preserve">def fetch_quiz_data():
+    """Fetch questions and answers from an Excel file stored in a GitHub repository."""
+    url = f"https://raw.githubusercontent.com/{GITHUB_REPO}/main/{GITHUB_FILE_PATH}"
+    # Force refresh by adding a unique query string (to bypass cache)
+    url += f"?timestamp={pd.Timestamp.now().timestamp()}"
+    try:
+        response = requests.get(url)
+        if response.status_code == 200:
+            quiz_data = pd.read_excel(io.BytesIO(response.content), dtype=str)  # Read as strings to preserve formatting
+            return quiz_data
+        else:
+            st.error(f"❌ Failed to fetch quiz data. Status Code: {response.status_code}")
+            return None
+    except Exception as e:
+        st.error(f"❌ Error fetching quiz data: {e}")
+        return None
+</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Question</t>
   </si>
@@ -34,35 +34,22 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t xml:space="preserve">def fetch_quiz_data():
-    """Fetch questions and answers from an Excel file stored in a GitHub repository."""
-    url = f"https://raw.githubusercontent.com/{GITHUB_REPO}/main/{GITHUB_FILE_PATH}"
-    # Force refresh by adding a unique query string (to bypass cache)
-    url += f"?timestamp={pd.Timestamp.now().timestamp()}"
-    try:
-        response = requests.get(url)
-        if response.status_code == 200:
-            quiz_data = pd.read_excel(io.BytesIO(response.content), dtype=str)  # Read as strings to preserve formatting
-            return quiz_data
-        else:
-            st.error(f"❌ Failed to fetch quiz data. Status Code: {response.status_code}")
-            return None
-    except Exception as e:
-        st.error(f"❌ Error fetching quiz data: {e}")
-        return None
-</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>hlk</t>
+  </si>
+  <si>
+    <t>klm</t>
+  </si>
+  <si>
+    <t>kjm</t>
+  </si>
+  <si>
+    <t>kmll,</t>
+  </si>
+  <si>
+    <t>jhbn</t>
+  </si>
+  <si>
+    <t>km,</t>
   </si>
 </sst>
 </file>
@@ -466,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Question</t>
   </si>
@@ -34,22 +34,22 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>hlk</t>
-  </si>
-  <si>
-    <t>klm</t>
-  </si>
-  <si>
-    <t>kjm</t>
-  </si>
-  <si>
-    <t>kmll,</t>
-  </si>
-  <si>
-    <t>jhbn</t>
-  </si>
-  <si>
-    <t>km,</t>
+    <t>What is the capital of India?
+{
+printf("Hello");
+}</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Agra</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Kolkatta</t>
   </si>
 </sst>
 </file>
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>Question</t>
   </si>
@@ -34,22 +34,25 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>What is the capital of India?
-{
-printf("Hello");
-}</t>
-  </si>
-  <si>
-    <t>Delhi</t>
-  </si>
-  <si>
-    <t>Agra</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>Kolkatta</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -441,19 +444,59 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Question</t>
   </si>
@@ -34,22 +34,49 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>What is capital of India?
+{
+printf("Hello");
+}</t>
+  </si>
+  <si>
+    <t>What is Ap capital?</t>
+  </si>
+  <si>
+    <t>Who is President of India?</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>a</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>Sikkim</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>K</t>
   </si>
   <si>
     <t>d</t>
@@ -447,13 +474,13 @@
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
@@ -464,19 +491,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -484,19 +511,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>Question</t>
   </si>
@@ -34,52 +34,151 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>What is capital of India?
-{
-printf("Hello");
-}</t>
-  </si>
-  <si>
-    <t>What is Ap capital?</t>
-  </si>
-  <si>
-    <t>Who is President of India?</t>
-  </si>
-  <si>
-    <t>Delhi</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>Sikkim</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>Kerala</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>d</t>
+    <t>Who is the President of India?</t>
+  </si>
+  <si>
+    <t>Where is the R.V.R. &amp; J.C. College of Engineering Located?</t>
+  </si>
+  <si>
+    <t>Who is the Prime Minister of USA?</t>
+  </si>
+  <si>
+    <t>How many Branches are there  in R.V.R. &amp; J.C. College of Engineering?</t>
+  </si>
+  <si>
+    <t>Who is the Father of Nation?</t>
+  </si>
+  <si>
+    <t>Most Recent Movie of Mahesh Babu which was Re-released?</t>
+  </si>
+  <si>
+    <t>What is the name of Director of Bahubali?</t>
+  </si>
+  <si>
+    <t>Who had written the song "Naatu Naatu"?</t>
+  </si>
+  <si>
+    <t>Who is the Music Director of PUSHPA?</t>
+  </si>
+  <si>
+    <t>Who is the Best Actor in Tollywood?</t>
+  </si>
+  <si>
+    <t>Sardar Vallabhai Patel</t>
+  </si>
+  <si>
+    <t>Vijayawada</t>
+  </si>
+  <si>
+    <t>Joe Biden</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Jawaharlal Nehru</t>
+  </si>
+  <si>
+    <t>Athadu</t>
+  </si>
+  <si>
+    <t>VV Vinayak</t>
+  </si>
+  <si>
+    <t>Anantha Sriram</t>
+  </si>
+  <si>
+    <t>DSP</t>
+  </si>
+  <si>
+    <t>Pawan Kalyan</t>
+  </si>
+  <si>
+    <t>Narendra Modi</t>
+  </si>
+  <si>
+    <t>Jaggayyapeta</t>
+  </si>
+  <si>
+    <t>Donald Trump</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Mahatma Gandhi</t>
+  </si>
+  <si>
+    <t>Seethamma Vaakitlo Sirimalle Chettu</t>
+  </si>
+  <si>
+    <t>Ram Gopal Varma</t>
+  </si>
+  <si>
+    <t>Chandra Bose</t>
+  </si>
+  <si>
+    <t>Thaman</t>
+  </si>
+  <si>
+    <t>NTR</t>
+  </si>
+  <si>
+    <t>Draupadi Murmu</t>
+  </si>
+  <si>
+    <t>Guntur</t>
+  </si>
+  <si>
+    <t>Ivanka Trump</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Pokiri</t>
+  </si>
+  <si>
+    <t>Raja Mouli</t>
+  </si>
+  <si>
+    <t>Sirivennela Seetha Rama Sastry</t>
+  </si>
+  <si>
+    <t>Mani Sharma</t>
+  </si>
+  <si>
+    <t>Mahesh Babu</t>
+  </si>
+  <si>
+    <t>Venkayya Naidu</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Kamala Harris</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Bal Gangadhar Tilak</t>
+  </si>
+  <si>
+    <t>Aagadu</t>
+  </si>
+  <si>
+    <t>Boyapati Srinivas</t>
+  </si>
+  <si>
+    <t>Keeravani</t>
+  </si>
+  <si>
+    <t>Ilayaraja</t>
+  </si>
+  <si>
+    <t>Allu Arjun</t>
   </si>
 </sst>
 </file>
@@ -440,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -471,19 +570,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -491,19 +590,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -511,19 +610,159 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Question</t>
   </si>
@@ -34,151 +34,19 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>Who is the President of India?</t>
-  </si>
-  <si>
-    <t>Where is the R.V.R. &amp; J.C. College of Engineering Located?</t>
-  </si>
-  <si>
-    <t>Who is the Prime Minister of USA?</t>
-  </si>
-  <si>
-    <t>How many Branches are there  in R.V.R. &amp; J.C. College of Engineering?</t>
-  </si>
-  <si>
-    <t>Who is the Father of Nation?</t>
-  </si>
-  <si>
-    <t>Most Recent Movie of Mahesh Babu which was Re-released?</t>
-  </si>
-  <si>
-    <t>What is the name of Director of Bahubali?</t>
-  </si>
-  <si>
-    <t>Who had written the song "Naatu Naatu"?</t>
-  </si>
-  <si>
-    <t>Who is the Music Director of PUSHPA?</t>
-  </si>
-  <si>
-    <t>Who is the Best Actor in Tollywood?</t>
-  </si>
-  <si>
-    <t>Sardar Vallabhai Patel</t>
-  </si>
-  <si>
-    <t>Vijayawada</t>
-  </si>
-  <si>
-    <t>Joe Biden</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Jawaharlal Nehru</t>
-  </si>
-  <si>
-    <t>Athadu</t>
-  </si>
-  <si>
-    <t>VV Vinayak</t>
-  </si>
-  <si>
-    <t>Anantha Sriram</t>
-  </si>
-  <si>
-    <t>DSP</t>
-  </si>
-  <si>
-    <t>Pawan Kalyan</t>
-  </si>
-  <si>
-    <t>Narendra Modi</t>
-  </si>
-  <si>
-    <t>Jaggayyapeta</t>
-  </si>
-  <si>
-    <t>Donald Trump</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Mahatma Gandhi</t>
-  </si>
-  <si>
-    <t>Seethamma Vaakitlo Sirimalle Chettu</t>
-  </si>
-  <si>
-    <t>Ram Gopal Varma</t>
-  </si>
-  <si>
-    <t>Chandra Bose</t>
-  </si>
-  <si>
-    <t>Thaman</t>
-  </si>
-  <si>
-    <t>NTR</t>
-  </si>
-  <si>
-    <t>Draupadi Murmu</t>
-  </si>
-  <si>
-    <t>Guntur</t>
-  </si>
-  <si>
-    <t>Ivanka Trump</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Pokiri</t>
-  </si>
-  <si>
-    <t>Raja Mouli</t>
-  </si>
-  <si>
-    <t>Sirivennela Seetha Rama Sastry</t>
-  </si>
-  <si>
-    <t>Mani Sharma</t>
-  </si>
-  <si>
-    <t>Mahesh Babu</t>
-  </si>
-  <si>
-    <t>Venkayya Naidu</t>
-  </si>
-  <si>
-    <t>Kolkata</t>
-  </si>
-  <si>
-    <t>Kamala Harris</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Bal Gangadhar Tilak</t>
-  </si>
-  <si>
-    <t>Aagadu</t>
-  </si>
-  <si>
-    <t>Boyapati Srinivas</t>
-  </si>
-  <si>
-    <t>Keeravani</t>
-  </si>
-  <si>
-    <t>Ilayaraja</t>
-  </si>
-  <si>
-    <t>Allu Arjun</t>
+    <t>Who is Ex CM of AP?</t>
+  </si>
+  <si>
+    <t>CBN</t>
+  </si>
+  <si>
+    <t>JGN</t>
+  </si>
+  <si>
+    <t>PSPK</t>
+  </si>
+  <si>
+    <t>KAPAL</t>
   </si>
 </sst>
 </file>
@@ -539,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -570,199 +438,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -34,19 +34,19 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>Who is Ex CM of AP?</t>
-  </si>
-  <si>
-    <t>CBN</t>
-  </si>
-  <si>
-    <t>JGN</t>
-  </si>
-  <si>
-    <t>PSPK</t>
-  </si>
-  <si>
-    <t>KAPAL</t>
+    <t>Which of these is not a Java keyword?</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>void</t>
+  </si>
+  <si>
+    <t>private</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
 </sst>
 </file>
@@ -450,7 +450,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Question</t>
   </si>
@@ -34,35 +34,217 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>Which of these is not a Java keyword?</t>
-  </si>
-  <si>
-    <t>static</t>
-  </si>
-  <si>
-    <t>void</t>
-  </si>
-  <si>
-    <t>private</t>
-  </si>
-  <si>
-    <t>Boolean</t>
+    <t>What is the correct way to create a variable in Python?
+a) var x = 10
+b) int x = 10
+c) x = 10
+d) declare x = 10</t>
+  </si>
+  <si>
+    <t>Which of the following is a valid variable name?</t>
+  </si>
+  <si>
+    <t>Python is a:</t>
+  </si>
+  <si>
+    <t>What is the output of print("Hello" + "World")?</t>
+  </si>
+  <si>
+    <t>Which function is used to display output in Python?</t>
+  </si>
+  <si>
+    <t>Which of the following is a list?</t>
+  </si>
+  <si>
+    <t>Lists are:</t>
+  </si>
+  <si>
+    <t>What is the output of:
+a = [1,2,3]
+a.append(4)
+print(a)</t>
+  </si>
+  <si>
+    <t>Strings in Python are enclosed in:</t>
+  </si>
+  <si>
+    <t>What is the output of:
+print("Python"[0])</t>
+  </si>
+  <si>
+    <t>Dictionary stores data in:</t>
+  </si>
+  <si>
+    <t>Which is a valid dictionary?</t>
+  </si>
+  <si>
+    <t>Tuples are:</t>
+  </si>
+  <si>
+    <t>lst = [10, 20, 30]
+for i in lst:
+    print(i,end=' ')</t>
+  </si>
+  <si>
+    <t>Which is a tuple?</t>
+  </si>
+  <si>
+    <t>var x=10</t>
+  </si>
+  <si>
+    <t>1name</t>
+  </si>
+  <si>
+    <t>Compiled language</t>
+  </si>
+  <si>
+    <t>Hello World</t>
+  </si>
+  <si>
+    <t>echo()</t>
+  </si>
+  <si>
+    <t>(1,2,3)</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>[1,2,3]</t>
+  </si>
+  <si>
+    <t>{ }</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Index form</t>
+  </si>
+  <si>
+    <t>{1,2,3}</t>
+  </si>
+  <si>
+    <t>Mutable</t>
+  </si>
+  <si>
+    <t>10 20 30</t>
+  </si>
+  <si>
+    <t>int x=10</t>
+  </si>
+  <si>
+    <t>name_1</t>
+  </si>
+  <si>
+    <t>Interpreted language</t>
+  </si>
+  <si>
+    <t>HelloWorld</t>
+  </si>
+  <si>
+    <t>display()</t>
+  </si>
+  <si>
+    <t>[1,2,3,4]</t>
+  </si>
+  <si>
+    <t>[ ]</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Key-value pairs</t>
+  </si>
+  <si>
+    <t>["a":1]</t>
+  </si>
+  <si>
+    <t>10 30 20</t>
+  </si>
+  <si>
+    <t>x=10</t>
+  </si>
+  <si>
+    <t>name-1</t>
+  </si>
+  <si>
+    <t>Assembly language</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>print()</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>"" or ''</t>
+  </si>
+  <si>
+    <t>Random order</t>
+  </si>
+  <si>
+    <t>{"a":1}</t>
+  </si>
+  <si>
+    <t>Editable</t>
+  </si>
+  <si>
+    <t>10 10 10</t>
+  </si>
+  <si>
+    <t>declare x=10</t>
+  </si>
+  <si>
+    <t>@name</t>
+  </si>
+  <si>
+    <t>Machine language</t>
+  </si>
+  <si>
+    <t>Hello+World</t>
+  </si>
+  <si>
+    <t>show()</t>
+  </si>
+  <si>
+    <t>&lt;1,2,3&gt;</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>&lt;&gt;</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Tuple form</t>
+  </si>
+  <si>
+    <t>(1:"a")</t>
+  </si>
+  <si>
+    <t>Changeable</t>
+  </si>
+  <si>
+    <t>20 30 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -78,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,32 +268,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -407,29 +571,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -438,19 +602,299 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
   <si>
     <t>Question</t>
   </si>
@@ -34,209 +34,230 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>What is the correct way to create a variable in Python?
-a) var x = 10
-b) int x = 10
-c) x = 10
-d) declare x = 10</t>
-  </si>
-  <si>
-    <t>Which of the following is a valid variable name?</t>
-  </si>
-  <si>
-    <t>Python is a:</t>
-  </si>
-  <si>
-    <t>What is the output of print("Hello" + "World")?</t>
-  </si>
-  <si>
-    <t>Which function is used to display output in Python?</t>
-  </si>
-  <si>
-    <t>Which of the following is a list?</t>
-  </si>
-  <si>
-    <t>Lists are:</t>
-  </si>
-  <si>
-    <t>What is the output of:
-a = [1,2,3]
-a.append(4)
+    <t>Which of the following is an invalid variable name in Python?</t>
+  </si>
+  <si>
+    <t>What will be the output of the following code?
+text = 'python'
+print(text.capitalize())</t>
+  </si>
+  <si>
+    <t>Which statement correctly describes the difference between a List and a Tuple?</t>
+  </si>
+  <si>
+    <t>Predict the output:
+nums = [10, 20, 30, 40, 50]
+print(nums[1:4])</t>
+  </si>
+  <si>
+    <t>What happens when you add an existing element to a Set?</t>
+  </si>
+  <si>
+    <t>Predict the output:
+d = {'a': 1, 'b': 2}
+d['a'] = 100
+print(d['a'])</t>
+  </si>
+  <si>
+    <t>Which of the following is NOT a valid dictionary key?</t>
+  </si>
+  <si>
+    <t>Predict the output of this code snippet:
+a = [1, 2]
+b = a
+b.append(3)
 print(a)</t>
   </si>
   <si>
-    <t>Strings in Python are enclosed in:</t>
-  </si>
-  <si>
-    <t>What is the output of:
-print("Python"[0])</t>
-  </si>
-  <si>
-    <t>Dictionary stores data in:</t>
-  </si>
-  <si>
-    <t>Which is a valid dictionary?</t>
-  </si>
-  <si>
-    <t>Tuples are:</t>
-  </si>
-  <si>
-    <t>lst = [10, 20, 30]
-for i in lst:
-    print(i,end=' ')</t>
-  </si>
-  <si>
-    <t>Which is a tuple?</t>
-  </si>
-  <si>
-    <t>var x=10</t>
-  </si>
-  <si>
-    <t>1name</t>
-  </si>
-  <si>
-    <t>Compiled language</t>
-  </si>
-  <si>
-    <t>Hello World</t>
-  </si>
-  <si>
-    <t>echo()</t>
-  </si>
-  <si>
-    <t>(1,2,3)</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>[1,2,3]</t>
-  </si>
-  <si>
-    <t>{ }</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Index form</t>
-  </si>
-  <si>
-    <t>{1,2,3}</t>
-  </si>
-  <si>
-    <t>Mutable</t>
-  </si>
-  <si>
-    <t>10 20 30</t>
-  </si>
-  <si>
-    <t>int x=10</t>
-  </si>
-  <si>
-    <t>name_1</t>
-  </si>
-  <si>
-    <t>Interpreted language</t>
-  </si>
-  <si>
-    <t>HelloWorld</t>
-  </si>
-  <si>
-    <t>display()</t>
-  </si>
-  <si>
-    <t>[1,2,3,4]</t>
-  </si>
-  <si>
-    <t>[ ]</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>Key-value pairs</t>
-  </si>
-  <si>
-    <t>["a":1]</t>
-  </si>
-  <si>
-    <t>10 30 20</t>
-  </si>
-  <si>
-    <t>x=10</t>
-  </si>
-  <si>
-    <t>name-1</t>
-  </si>
-  <si>
-    <t>Assembly language</t>
+    <t>How do you create an empty set in Python?</t>
+  </si>
+  <si>
+    <t>Predict the output:
+s = 'Hello'
+print(s * 2)</t>
+  </si>
+  <si>
+    <t>Which method would you use to remove and return the last element of a list?</t>
+  </si>
+  <si>
+    <t>What is the output of the following?
+my_tuple = (1, 2, [3, 4])
+my_tuple[2][0] = 9
+print(my_tuple)</t>
+  </si>
+  <si>
+    <t>What is the result of len({1, 2, 2, 3, 3, 3})?</t>
+  </si>
+  <si>
+    <t>Predict the output:
+x = 5
+y = '10'
+print(str(x) + y)</t>
+  </si>
+  <si>
+    <t>How do you access the value associated with the key 'name' in a dictionary 'user'?</t>
+  </si>
+  <si>
+    <t>variable_name_2</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Tuples are mutable, while lists are immutable.</t>
+  </si>
+  <si>
+    <t>[10, 20, 30]</t>
+  </si>
+  <si>
+    <t>The set is converted into a list.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>[1, 2]</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
   <si>
     <t>Error</t>
   </si>
   <si>
-    <t>print()</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>"" or ''</t>
-  </si>
-  <si>
-    <t>Random order</t>
-  </si>
-  <si>
-    <t>{"a":1}</t>
-  </si>
-  <si>
-    <t>Editable</t>
-  </si>
-  <si>
-    <t>10 10 10</t>
-  </si>
-  <si>
-    <t>declare x=10</t>
-  </si>
-  <si>
-    <t>@name</t>
-  </si>
-  <si>
-    <t>Machine language</t>
-  </si>
-  <si>
-    <t>Hello+World</t>
-  </si>
-  <si>
-    <t>show()</t>
-  </si>
-  <si>
-    <t>&lt;1,2,3&gt;</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>&lt;&gt;</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>Tuple form</t>
-  </si>
-  <si>
-    <t>(1:"a")</t>
-  </si>
-  <si>
-    <t>Changeable</t>
-  </si>
-  <si>
-    <t>20 30 10</t>
+    <t>discard()</t>
+  </si>
+  <si>
+    <t>(1, 2, 9)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>user.name</t>
+  </si>
+  <si>
+    <t>2_variable_name</t>
+  </si>
+  <si>
+    <t>PYTHON</t>
+  </si>
+  <si>
+    <t>Tuples can store different data types, but lists cannot.</t>
+  </si>
+  <si>
+    <t>[20, 30, 40]</t>
+  </si>
+  <si>
+    <t>The set remains unchanged because sets only store unique elements.</t>
+  </si>
+  <si>
+    <t>KeyError</t>
+  </si>
+  <si>
+    <t>[1, 2, 3]</t>
+  </si>
+  <si>
+    <t>set({})</t>
+  </si>
+  <si>
+    <t>HelloHello</t>
+  </si>
+  <si>
+    <t>delete()</t>
+  </si>
+  <si>
+    <t>(1, 2, [9, 4])</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5 10</t>
+  </si>
+  <si>
+    <t>user{name}</t>
+  </si>
+  <si>
+    <t>VariableName</t>
+  </si>
+  <si>
+    <t>python</t>
+  </si>
+  <si>
+    <t>Lists are mutable, while tuples are immutable.</t>
+  </si>
+  <si>
+    <t>[10, 20, 30, 40]</t>
+  </si>
+  <si>
+    <t>The element is added a second time.</t>
+  </si>
+  <si>
+    <t>(1, 2, 3)</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>set()</t>
+  </si>
+  <si>
+    <t>Hello 2</t>
+  </si>
+  <si>
+    <t>pop()</t>
+  </si>
+  <si>
+    <t>(1, 2, [3, 4])</t>
+  </si>
+  <si>
+    <t>TypeError</t>
+  </si>
+  <si>
+    <t>user['name']</t>
+  </si>
+  <si>
+    <t>_variable_name</t>
+  </si>
+  <si>
+    <t>pYTHON</t>
+  </si>
+  <si>
+    <t>Lists use parentheses (), and tuples use square brackets [].</t>
+  </si>
+  <si>
+    <t>[20, 30, 40, 50]</t>
+  </si>
+  <si>
+    <t>An error is raised.</t>
+  </si>
+  <si>
+    <t>{'a': 100, 'b': 2}</t>
+  </si>
+  <si>
+    <t>'name'</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>HHeelllloo</t>
+  </si>
+  <si>
+    <t>remove()</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>user('name')</t>
   </si>
 </sst>
 </file>
@@ -608,13 +629,13 @@
         <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -628,13 +649,13 @@
         <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -648,13 +669,13 @@
         <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -668,10 +689,10 @@
         <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>38</v>
@@ -688,13 +709,13 @@
         <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -705,16 +726,16 @@
         <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -725,16 +746,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -745,16 +766,16 @@
         <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -765,16 +786,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -785,16 +806,16 @@
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -805,16 +826,16 @@
         <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -825,16 +846,16 @@
         <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -842,19 +863,19 @@
         <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -862,19 +883,19 @@
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -882,19 +903,19 @@
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="243">
   <si>
     <t>Question</t>
   </si>
@@ -34,19 +34,744 @@
     <t>Correct Answer</t>
   </si>
   <si>
-    <t>Hi</t>
-  </si>
-  <si>
-    <t>Hello</t>
-  </si>
-  <si>
-    <t>welcome</t>
-  </si>
-  <si>
-    <t>ms</t>
-  </si>
-  <si>
-    <t>nj</t>
+    <t>Which component of the Java environment is responsible for running the compiled bytecode?</t>
+  </si>
+  <si>
+    <t>What is the default value of a boolean primitive instance variable in Java?</t>
+  </si>
+  <si>
+    <t>What is the valid range of values for a byte data type in Java?</t>
+  </si>
+  <si>
+    <t>Which keyword is used to declare a constant variable in Java?</t>
+  </si>
+  <si>
+    <t>What happens during type casting from double to int in Java?</t>
+  </si>
+  <si>
+    <t>What will be the output of the expression 5 + 2 * 3 in Java?</t>
+  </si>
+  <si>
+    <t>Which operator is used for bitwise XOR in Java?</t>
+  </si>
+  <si>
+    <t>What is the result of the arithmetic operation 10 % 3?</t>
+  </si>
+  <si>
+    <t>Consider the code: int a = 5; int b = a++;. What are the values of a and b after execution?</t>
+  </si>
+  <si>
+    <t>Which of the following is a short-circuit logical operator in Java?</t>
+  </si>
+  <si>
+    <t>What type of expression must be placed inside the condition of an if statement in Java?</t>
+  </si>
+  <si>
+    <t>What will the following snippet print?
+int x = 10;
+if (x &gt; 10) {
+    System.out.print("A");
+} else if (x == 10) {
+    System.out.print("B");
+} else {
+    System.out.print("C");
+}</t>
+  </si>
+  <si>
+    <t>Which ternary expression is equivalent to if (a &gt; b) max = a; else max = b;?</t>
+  </si>
+  <si>
+    <t>What happens when multiple else-if conditions evaluate to true?</t>
+  </si>
+  <si>
+    <t>What will be the output of this code?
+boolean flag = false;
+if (flag = true) {
+    System.out.print("Yes");
+} else {
+    System.out.print("No");
+}</t>
+  </si>
+  <si>
+    <t>Which data type was NOT supported in switch statements prior to Java 7?</t>
+  </si>
+  <si>
+    <t>What occurs if a break statement is omitted at the end of a matching case block in a standard switch?</t>
+  </si>
+  <si>
+    <t>Is the default block mandatory inside a Java switch statement?</t>
+  </si>
+  <si>
+    <t>What is the output of the following block?
+int day = 2;
+switch (day) {
+    case 1: System.out.print("One ");
+    case 2: System.out.print("Two ");
+    case 3: System.out.print("Three ");
+            break;
+    default: System.out.print("Default");
+}</t>
+  </si>
+  <si>
+    <t>What kind of expression can be used as a label for a case inside a switch statement?</t>
+  </si>
+  <si>
+    <t>Which loop construct guarantees that its body will execute at least once?</t>
+  </si>
+  <si>
+    <t>How many times will the following loop execute?
+for (int i = 0; i &lt; 5; i += 2) {
+    // block
+}</t>
+  </si>
+  <si>
+    <t>Which statement is used to skip the rest of the current iteration of a loop and move directly to the next pass?</t>
+  </si>
+  <si>
+    <t>What will be the final value of count after this loop finishes execution?
+int count = 0;
+while (count &lt; 3) {
+    count++;
+}</t>
+  </si>
+  <si>
+    <t>What is a key characteristic of the enhanced for loop (for-each)?</t>
+  </si>
+  <si>
+    <t>What is an instance of a class called in Java?</t>
+  </si>
+  <si>
+    <t>Which keyword is used to dynamically allocate memory for an object?</t>
+  </si>
+  <si>
+    <t>What is the return type specified for a constructor in Java?</t>
+  </si>
+  <si>
+    <t>If no constructor is explicitly written in a class, what does the Java compiler supply?</t>
+  </si>
+  <si>
+    <t>Which keyword is used within a class to refer to the current instance object?</t>
+  </si>
+  <si>
+    <t>What is Encapsulation in OOP?</t>
+  </si>
+  <si>
+    <t>Which access modifier restricts member access exclusively to within the defining class itself?</t>
+  </si>
+  <si>
+    <t>How do you implement read-only access for a private field in a class?</t>
+  </si>
+  <si>
+    <t>Which access modifier allows members to be accessed by subclasses located in a different package?</t>
+  </si>
+  <si>
+    <t>What is a primary practical benefit of using getter and setter methods?</t>
+  </si>
+  <si>
+    <t>Which keyword does a child class use to inherit from a parent class in Java?</t>
+  </si>
+  <si>
+    <t>Does Java support multiple inheritance using classes (e.g., class C extends A, B)?</t>
+  </si>
+  <si>
+    <t>Which keyword is used inside a subclass constructor to invoke a constructor of its parent class?</t>
+  </si>
+  <si>
+    <t>What structural relationship does class inheritance represent?</t>
+  </si>
+  <si>
+    <t>What happens if a class is defined with the final modifier?</t>
+  </si>
+  <si>
+    <t>What defines Method Overloading in Java?</t>
+  </si>
+  <si>
+    <t>Method Overriding is an example of which form of polymorphism?</t>
+  </si>
+  <si>
+    <t>Which rule must be followed when overriding a method in a subclass?</t>
+  </si>
+  <si>
+    <t>Can static methods be overridden in Java?</t>
+  </si>
+  <si>
+    <t>What happens if two methods in a class have identical names and identical parameters, but different return types?</t>
+  </si>
+  <si>
+    <t>Can an abstract class be instantiated directly using the new operator?</t>
+  </si>
+  <si>
+    <t>Which keyword is used by a class to implement an interface in Java?</t>
+  </si>
+  <si>
+    <t>By default, fields declared inside a standard Java Interface are implicitly:</t>
+  </si>
+  <si>
+    <t>Starting from Java 8, interfaces can contain concrete methods with bodies by using which modifier keyword?</t>
+  </si>
+  <si>
+    <t>What is a key capability difference between an abstract class and an interface in Java?</t>
+  </si>
+  <si>
+    <t>JDK</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>-128 to 127</t>
+  </si>
+  <si>
+    <t>const</t>
+  </si>
+  <si>
+    <t>The value is rounded to the nearest integer.</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>&amp;</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>a = 5, b = 5</t>
+  </si>
+  <si>
+    <t>Any integer expression</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>max = (a &gt; b) ? b : a;</t>
+  </si>
+  <si>
+    <t>All matching blocks execute.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>A compilation error occurs.</t>
+  </si>
+  <si>
+    <t>Yes, it must be the first statement.</t>
+  </si>
+  <si>
+    <t>Two</t>
+  </si>
+  <si>
+    <t>A dynamic variable changed at runtime</t>
+  </si>
+  <si>
+    <t>for loop</t>
+  </si>
+  <si>
+    <t>5 times</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>It iterates backwards easily.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>alloc</t>
+  </si>
+  <si>
+    <t>void</t>
+  </si>
+  <si>
+    <t>A parameterized constructor</t>
+  </si>
+  <si>
+    <t>super</t>
+  </si>
+  <si>
+    <t>Deriving new classes from existing parent classes</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>Provide a public setter method only</t>
+  </si>
+  <si>
+    <t>private</t>
+  </si>
+  <si>
+    <t>It increases execution speed at compile-time.</t>
+  </si>
+  <si>
+    <t>implements</t>
+  </si>
+  <si>
+    <t>Yes, for all concrete classes</t>
+  </si>
+  <si>
+    <t>this()</t>
+  </si>
+  <si>
+    <t>HAS-A relationship</t>
+  </si>
+  <si>
+    <t>It cannot be instantiated using new.</t>
+  </si>
+  <si>
+    <t>Writing a method in a subclass with the same signature as one in the superclass</t>
+  </si>
+  <si>
+    <t>Compile-time polymorphism</t>
+  </si>
+  <si>
+    <t>The method parameters must be changed.</t>
+  </si>
+  <si>
+    <t>Yes, freely like instance methods.</t>
+  </si>
+  <si>
+    <t>Method overloading functions normally.</t>
+  </si>
+  <si>
+    <t>Yes, without any restrictions.</t>
+  </si>
+  <si>
+    <t>extends</t>
+  </si>
+  <si>
+    <t>private and final</t>
+  </si>
+  <si>
+    <t>abstract</t>
+  </si>
+  <si>
+    <t>Abstract classes cannot have constructors, but interfaces can.</t>
+  </si>
+  <si>
+    <t>JRE</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>-32768 to 32767</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>The fractional part is truncated (dropped).</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>a = 6, b = 6</t>
+  </si>
+  <si>
+    <t>&amp;&amp;</t>
+  </si>
+  <si>
+    <t>Strictly a boolean expression</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>max = (a &gt; b) ? a : b;</t>
+  </si>
+  <si>
+    <t>Only the first matching block executes.</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Execution falls through to the next case block unconditionally.</t>
+  </si>
+  <si>
+    <t>Yes, it must be the last statement.</t>
+  </si>
+  <si>
+    <t>Two Three</t>
+  </si>
+  <si>
+    <t>A compile-time constant expression</t>
+  </si>
+  <si>
+    <t>while loop</t>
+  </si>
+  <si>
+    <t>3 times</t>
+  </si>
+  <si>
+    <t>continue</t>
+  </si>
+  <si>
+    <t>It traverses collections or arrays without needing an index variable.</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>malloc</t>
+  </si>
+  <si>
+    <t>A default no-argument constructor</t>
+  </si>
+  <si>
+    <t>this</t>
+  </si>
+  <si>
+    <t>Bundling data (variables) and methods together while restricting direct external access</t>
+  </si>
+  <si>
+    <t>protected</t>
+  </si>
+  <si>
+    <t>Provide a public getter method only</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>It provides validation and control over how instance variables are modified.</t>
+  </si>
+  <si>
+    <t>Yes, provided both parent classes are abstract</t>
+  </si>
+  <si>
+    <t>super()</t>
+  </si>
+  <si>
+    <t>IS-A relationship</t>
+  </si>
+  <si>
+    <t>It cannot be extended by any other class.</t>
+  </si>
+  <si>
+    <t>Having multiple methods in the same class with the same name but different parameters</t>
+  </si>
+  <si>
+    <t>Runtime polymorphism (Dynamic method dispatch)</t>
+  </si>
+  <si>
+    <t>The method signature (name and parameters) must match the superclass method exactly.</t>
+  </si>
+  <si>
+    <t>No, static methods are bound at compile time and are hidden rather than overridden.</t>
+  </si>
+  <si>
+    <t>A compile-time error occurs.</t>
+  </si>
+  <si>
+    <t>No, abstract classes cannot be instantiated directly.</t>
+  </si>
+  <si>
+    <t>protected and static</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>A class can implement multiple interfaces, but can extend only one class.</t>
+  </si>
+  <si>
+    <t>JVM</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0 to 255</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>A compile-time error occurs automatically.</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>^</t>
+  </si>
+  <si>
+    <t>a = 6, b = 5</t>
+  </si>
+  <si>
+    <t>Any non-null object reference</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>max = (a &lt; b) ? a : b;</t>
+  </si>
+  <si>
+    <t>Only the last matching block executes.</t>
+  </si>
+  <si>
+    <t>Compilation Error</t>
+  </si>
+  <si>
+    <t>char</t>
+  </si>
+  <si>
+    <t>The switch statement terminates immediately.</t>
+  </si>
+  <si>
+    <t>No, it is optional.</t>
+  </si>
+  <si>
+    <t>One Two Three</t>
+  </si>
+  <si>
+    <t>A method call returning a double</t>
+  </si>
+  <si>
+    <t>do-while loop</t>
+  </si>
+  <si>
+    <t>2 times</t>
+  </si>
+  <si>
+    <t>skip</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>It allows modifying the length of the array safely during iteration.</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>The class type itself</t>
+  </si>
+  <si>
+    <t>A static constructor</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>Overloading methods based on parameter signatures</t>
+  </si>
+  <si>
+    <t>Declare the field as protected</t>
+  </si>
+  <si>
+    <t>It prevents memory leak exceptions.</t>
+  </si>
+  <si>
+    <t>inherits</t>
+  </si>
+  <si>
+    <t>No, Java avoids potential ambiguity (the Diamond Problem) by disallowing it</t>
+  </si>
+  <si>
+    <t>parent()</t>
+  </si>
+  <si>
+    <t>USES-A relationship</t>
+  </si>
+  <si>
+    <t>All of its methods must be static.</t>
+  </si>
+  <si>
+    <t>Changing only the return type of a method without altering its arguments</t>
+  </si>
+  <si>
+    <t>Static polymorphism</t>
+  </si>
+  <si>
+    <t>The access level must be made more restrictive than the parent class.</t>
+  </si>
+  <si>
+    <t>Yes, but only if they belong to abstract classes.</t>
+  </si>
+  <si>
+    <t>The program runs and selects the return type dynamically.</t>
+  </si>
+  <si>
+    <t>Yes, provided it contains no abstract methods.</t>
+  </si>
+  <si>
+    <t>uses</t>
+  </si>
+  <si>
+    <t>public, static, and final</t>
+  </si>
+  <si>
+    <t>concrete</t>
+  </si>
+  <si>
+    <t>Interfaces can hold instance state variables, whereas abstract classes cannot.</t>
+  </si>
+  <si>
+    <t>JAVAC</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>-2147483648 to 2147483647</t>
+  </si>
+  <si>
+    <t>immutable</t>
+  </si>
+  <si>
+    <t>The value wraps around zero.</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>a = 5, b = 6</t>
+  </si>
+  <si>
+    <t>!</t>
+  </si>
+  <si>
+    <t>Any non-zero numeric value</t>
+  </si>
+  <si>
+    <t>max = (a == b) ? a : b;</t>
+  </si>
+  <si>
+    <t>A runtime exception is thrown.</t>
+  </si>
+  <si>
+    <t>Runtime Error</t>
+  </si>
+  <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>The default block executes twice.</t>
+  </si>
+  <si>
+    <t>Yes, but only when switching on integer values.</t>
+  </si>
+  <si>
+    <t>Two Three Default</t>
+  </si>
+  <si>
+    <t>A boolean condition like case (x &gt; 5):</t>
+  </si>
+  <si>
+    <t>Enhanced for loop</t>
+  </si>
+  <si>
+    <t>Infinite times</t>
+  </si>
+  <si>
+    <t>goto</t>
+  </si>
+  <si>
+    <t>It can only be used with primitive data types.</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>create</t>
+  </si>
+  <si>
+    <t>Constructors do not have any return type</t>
+  </si>
+  <si>
+    <t>A private constructor</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>Executing code dynamically at runtime</t>
+  </si>
+  <si>
+    <t>Default (package-private)</t>
+  </si>
+  <si>
+    <t>Declare the class as abstract</t>
+  </si>
+  <si>
+    <t>It enforces automatic multi-threading safety.</t>
+  </si>
+  <si>
+    <t>Yes, using the multi access keyword</t>
+  </si>
+  <si>
+    <t>base()</t>
+  </si>
+  <si>
+    <t>DEPENDS-ON relationship</t>
+  </si>
+  <si>
+    <t>Its variables become volatile automatically.</t>
+  </si>
+  <si>
+    <t>Marking a method as static inside an interface</t>
+  </si>
+  <si>
+    <t>Parametric polymorphism</t>
+  </si>
+  <si>
+    <t>The overridden method must be marked static.</t>
+  </si>
+  <si>
+    <t>Yes, if annotated with @Override.</t>
+  </si>
+  <si>
+    <t>The compiler ignores the second method definition.</t>
+  </si>
+  <si>
+    <t>Yes, if instantiated inside a static context.</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>package-private and volatile</t>
+  </si>
+  <si>
+    <t>virtual</t>
+  </si>
+  <si>
+    <t>Abstract classes cannot contain any implemented concrete methods.</t>
   </si>
 </sst>
 </file>
@@ -381,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="30.7109375" style="1" customWidth="1"/>
@@ -412,19 +1137,999 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+      <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
